--- a/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-technical-qa.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -36,21 +36,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">持久化矩阵乘里，tile 循环套着 K 循环，K 循环用 num_stages 做软件流水。在 tile 循环的 tl.range 上写 flatten=True 后，编译器做了什么？每个 CTA 省掉了什么、省不掉什么、代价是什么？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，持久化矩阵乘的 tile 循环套着 K 循环，K 循环用 num_stages 做软件流水（读入比乘加提前几轮发出）。在 tile 循环的 tl.range 上写 flatten=True、合并生效后，每个 CTA 省掉了什么，又省不掉什么？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：编译器把两层循环合成一层，软件流水于是能跨过 tile 的边界：下一个 tile 的读入在当前 tile 还没算完时就已发出。
-• [T#B#省掉]：流水的预热与排空从每个 tile 一次变成每个 CTA 一次，tile 边界上等第一批数据的空档消失。
-• [T#B#省不掉]：tile 自己的 prologue（算坐标）与 epilogue（写回）仍是每个 tile 一次，合并后它们变成循环体里的两个条件分支（scf.if）。
-• [T#B#代价]：epilogue 执行时下一个 tile 的输入已在路上、输入缓冲仍被占着，写回用的中转缓冲不能再借用空出的输入槽，共享内存多一档。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：省掉的是流水的预热与排空：两层循环合成一层后，流水能跨过 tile 边界，预热与排空从每个 tile 一次变成每个 CTA 一次；省不掉的是 tile 自己的 prologue 与 epilogue，仍是每个 tile 一次。
+• [T#B#原因]：流水只在一个循环内部生效。不合并时每个 tile 的 K 循环一结束就排空，下一个 tile 要重新发出头几轮读入、等第一批数据到达；合并后，下一个 tile 的头几轮读入在当前 tile 的最后几轮乘加期间就已发出。
+• [T#B#省不掉]：prologue（算 tile 坐标和偏移、把累加器清零）与 epilogue（转成 fp16、写回）是每个 tile 自己的计算，合并只是把它们挪进循环体按条件执行，仍由同一批 warp 来做。
 [T#B,!c47f17#边界]：它是请求不是保证：只有 tile 循环里直接套一个 K 循环、中间没有别的 if 或 while、内层边界不随外层变化（或用 tl.assume 说明至少执行一次）时才合并；不满足时不报错，原样保留两层循环。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">预热排空每 CTA 一次；prologue 与 epilogue 仍每 tile 一次；多一块中转</t>
+          <t xml:space="preserve">流水只管一个循环；预热排空每 CTA 一次；prologue 与 epilogue 仍每 tile 一次</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -62,26 +61,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">持久化矩阵乘里 B 按行主序 \[K, N\] 存放（沿 N 连续），A 是 \[M, K\]（沿 K 连续）。N 方向的下标 offset_n 在 tile 开头算好并加了连续性声明，K 方向的 offset_k 在 K 循环里算。flatten 关时 A、B 都是 16 字节异步拷贝；flatten 开时只剩 A 是，B 退回同步读入。为什么？怎样修？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的持久化矩阵乘里，B 按行主序 \[K, N\] 存放（沿 N 连续），A 是 \[M, K\]（沿 K 连续）。N 方向的下标 offset_n 在 tile 开头算好并加了连续性声明，K 方向的 offset_k 在 K 循环里算。flatten 关时 A、B 都是 16 字节异步拷贝；flatten 开时只剩 A 是，B 退回同步读入。为什么？怎样修？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：合并后 tile 开头的代码被包进一个 scf.if，offset_n 作为这个 if 的结果传出；流水挑选读入时看不到附在它上面的连续性声明，B 就不能成组搬。
-• [T#B#为何丢]：进入新 tile 的那一轮走 if 分支、带着声明；其余各轮沿用上一次的值。合并点上两边的信息取最大公约数，声明随之丢失。
+• [T#B#为何丢]：声明不产生新值，只挂在 if 里定义 offset_n 的那条操作上；K 循环用的是 if 传出的结果，不进 if 的各轮沿用旧值，这个结果上没有声明（这一因果由只编译的对照实验得出）。
 • [T#B#A 为何没事]：A 的连续方向是 K，offset_k 一直在每轮都执行的 K 循环体里计算，声明就在流水看得到的地方。
-• [T#B#修法]：把 B 连续方向的下标（连同它的改写与声明）挪进 K 循环里，由 tile 坐标重新计算。
-[T#B,!c47f17#边界]：只挪声明那一行没有用，声明贴在定义值的那条操作上；按 b.T 传入的 B 沿 K 连续，不受这个问题影响。</t>
+• [T#B#修法]：把 B 连续方向的下标（连同它的改写与声明）挪进 K 循环里，由 tile 坐标重新计算；写回时再由 tile 坐标另算一份，不沿用 K 循环里的这个值。
+[T#B,!c47f17#边界]：若在 K 循环里给循环前已有的 offset_n 重新赋值、写回又直接用这个跨轮传下来的值，flatten 开时提前量会消失（循环里的等待全是 num = 0）；按 b.T 传入的 B 沿 K 连续，不受这个问题影响。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prologue 的值经 scf.if 传出会丢声明；连续方向的下标在 K 循环里算</t>
+          <t xml:space="preserve">prologue 的值经 scf.if 传出会丢声明；连续方向的下标在 K 循环里算，写回另算一份</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 练习 R-03</t>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 练习 R-03、R-05</t>
         </is>
       </c>
     </row>
@@ -122,8 +121,9 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：flatten 改的是一条执行顺序里的先后，像单线程的异步；专用化增加执行顺序的条数，像多线程的生产者与消费者。
 • [T#B#flatten]：同一批 warp 仍按一条顺序执行，编译器把“发出下一个 tile 的读入”挪到当前 tile 最后几轮乘加之前，提前量固定为 num_stages − 1 轮。
 • [T#B#专用化]：另分一批 warp 只做搬运，它的程序里两次读入之间没有乘加和 epilogue，只要有空槽就发，提前量由缓冲大小决定。
-• [T#B#代价]：flatten 不加人手，只多一块中转缓冲，乘加与 epilogue 仍不能重叠；专用化要多发 warp（例如 8 个变 12 个），还要付屏障同步和更多缓冲（每个操作数从 S − 1 个槽变成 S 个）。
-[T#B,!c47f17#边界]：两者不互斥，都依赖异步拷贝；区别只在由谁、在什么时候安排发出读入。</t>
+• [T#B#代价]：flatten 不加 warp，只多一块写回中转；专用化要多发 warp、付屏障同步，还要占更多输入缓冲（例如 Triton 3.7.1 在 sm_120 上每个操作数由 2 个槽变为 3 个）。
+• [T#B#重叠]：flatten 下 epilogue 能否与下一个 tile 的乘加重叠，取决于乘加指令：同步的 mma.sync（sm_89、sm_120）和 epilogue 由同一批 warp 执行，只能一先一后；sm_100 的 tcgen05.mma 异步、累加器在 TMEM，Triton 3.7.1 不专用化时也给持久版开了两个累加器（只编译观察，未在设备上验证是否真的重叠）。
+[T#B,!c47f17#边界]：两者在概念上不互斥，都靠读入能在后台进行，区别只在由谁、在什么时候安排发出读入；但在 Triton 3.7.1 的 sm_90 上不能同时开启，教程在 Hopper 上开专用化时关掉了 flatten。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -140,12 +140,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">分块矩阵乘里，M、N、K 都可能不是块的整数倍。Triton 持久化矩阵乘教程对 M、N 方向的越界下标用 tl.where 改成 0，对 K 方向却用 mask 并让越界位置读成 0。为什么 M、N 可以“改成 0”，K 不行？M、N 方向为什么又非处理不可？</t>
+          <t xml:space="preserve">分块矩阵乘里，M、N、K 都可能不是块的整数倍。Triton 持久化矩阵乘教程对 M、N 方向的越界下标用 tl.where 改成 0，对 K 方向则用 mask 让越界位置读成 0。M、N 方向与 K 方向的越界位置各要保证什么？为什么两者不同？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：M、N 是自由维度，越界的行列只影响 C 的越界部分，写回时丢掉即可；K 是被求和的维度，越界位置的值会进入每个输出的和，必须读成 0。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：M、N 是自由维度，越界的行列只影响 C 的越界部分，写回时丢掉即可，读入时只需保证地址合法；K 是被求和的维度，越界位置的值会进入每个输出的和，必须读成 0。
 • [T#B#M、N]：下标改成 0 后读到的是第 0 行或第 0 列的真实数据，算出的结果落在越界的行列里，写回时被 mask 丢掉，只需保证地址合法。
 • [T#B#K]：若把 K 方向下标也改成 0，越界位置读到的是第 0 列的 A 和第 0 行的 B，每个输出都多加几份 a\[m,0\]·b\[0,n\]。
 • [T#B#为何要处理]：不处理时 tl.load 真的访问矩阵之外的地址，是未定义行为：可能读到别的分配而碰巧正确，也可能触发非法访问。
@@ -166,20 +166,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 编译器要知道下标张量的取值是否一路加一（取值连续度），才能决定能否成组读取。对 offs = pid_n * 64 + tl.arange(0, 64) 做 tl.where(offs &lt; N, offs, 0) 之后，编译器认定它的取值连续度只剩 1，读入因此退回逐元素。为什么？这是不是说值真的不连续了？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，编译器要知道下标张量的取值是否一路加一（取值连续度），才能决定能否成组读取。对 offs = pid_n * 64 + tl.arange(0, 64) 做 tl.where(offs &lt; N, offs, 0) 之后，编译器认定它的取值连续度只剩 1，读入因此退回逐元素。为什么会是 1？在完整的 tile 里，改写后的值实际是什么样？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：对 where（IR 里的 select），结果的取值连续度取 x、y 的取值连续度和条件的恒定度三者的最大公约数；y 是常量 0，取值连续度为 1，结果也就只剩 1。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：对 where（IR 里的 select），结果的取值连续度取 x 与 y 的取值连续度、条件的恒定度（每组多少个相邻元素取值相同）三者的最大公约数；y 是常量 0，取值连续度为 1，结果也就只剩 1。
 • [T#B#为什么取 gcd]：r\[i\] = cond\[i\] ? x\[i\] : y\[i\] 逐位置取值；编译时不知道 N，就不知道哪些位置取自 y，只能按对任何 N 都成立的方式记账：一组里混着取，或整组都取 y，都不连续。
-• [T#B#实际值]：完整的 tile 里 cond 全真，值照样一路加一；只有跨过边界的那个 tile 才会出现 192、193、…、0、0 这样的值。
-[T#B,!c47f17#边界]：这是保守结论，不是值真的乱了；只用 mask、不改写下标时，下标的取值连续度仍是 64，不需要声明。</t>
+• [T#B#实际值]：完整的 tile 里 cond 全真，值照样一路加一；只有跨过边界的那个 tile 才不连续，例如 N = 208 时第 3 号 tile 是 192…207 再跟 48 个 0。所以这是保守结论，不是值真的乱了。
+• [T#B#取值非存储]：这里的“连续”是取值连续：张量里存的数是不是 v, v+1, …，作为下标时指向的地址是否相邻；不是张量自己的存储连续（PyTorch 的 is_contiguous）。tl.where 构建的新张量存储没有问题，问题出在它的值上。
+[T#B,!c47f17#边界]：只用 mask、不改写下标时，下标的取值连续度仍是 64，不需要声明；连续度、整除度、恒定度和三个声明函数描述的都是取值上的性质。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">select 取 gcd；常量 0 的取值连续度是 1</t>
+          <t xml:space="preserve">select 取 gcd；常量 0 的取值连续度是 1；说的是取值，不是存储</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -191,17 +192,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">要用实测检验“持久化矩阵乘比逐 tile 发射快，而且优势随 K 增大而变小”。Triton 教程自带的 bench 让各 kernel 分别 autotune，持久版还同时带着 flatten，各版本先后连续跑。怎样设计测量，才能把速度差别归到某个具体改动上？</t>
+          <t xml:space="preserve">要用实测检验“持久化矩阵乘比逐 tile 发射快，而且优势随 K 增大而变小”。Triton 教程自带的 bench 直接比较教程里的各个 kernel，测出的速度差别归不到某一个改动上。为什么归不了？怎样设计测量才能做到？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：同一个 kernel、同一份输入，只改要比较的开关；交替测量、轮内相除，判据在测量前写定。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：同一个 kernel、同一份输入，先核对结果正确，只改要比较的开关；交替测量、轮内相除，判据在测量前写定。
+• [T#B#混杂]：教程的 bench 让各 kernel 分别 autotune，选出的配置可能不同；持久版还捆着 flatten；各版本先后连续跑，时钟和温度的漂移会落在后跑的版本上。
 • [T#B#控制变量]：块、stage、warp 数固定，不 autotune；三个版本只差调度（每个 CTA 一个 tile 对每个 SM 一个持久 CTA）和 flatten 两个开关。
 • [T#B#抵消漂移]：每一轮按轮换的顺序把各版本各测一次，比值先在同一轮内相除，再报各轮的中位数和四分位区间。
 • [T#B#拆因子]：只差调度的比值衡量持久化本身，只差 flatten 的比值衡量循环合并，两个开关同时变的总比值等于二者之积。
-• [T#B#正确性]：测量前逐项核对结果，性能结论另有独立的正确性证据。
-[T#B,!c47f17#边界]：这样能定位到是哪个开关，但一个开关内部的几项变化（例如持久化里的 CTA 分派、固定工作和调度方式）仍分不开。</t>
+[T#B,!c47f17#边界]：这样能定位到是哪个开关，但一个开关内部仍可能包含多项变化，测量只给出它们的净和。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -218,15 +219,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">检查一个 Triton 矩阵乘的 TTGIR：A、B 的读入都已经是 ttg.async_copy_global_to_local（异步拷贝），也没有同步的 tt.load。能否据此断定 K 循环有流水、读入提前发出了？还应该看什么？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中检查一个矩阵乘的 TTGIR：A、B 的读入都已经是 ttg.async_copy_global_to_local（异步拷贝），也没有同步的 tt.load。要确认 K 循环的读入真的提前发出了（有提前量），还应该看什么？为什么只看是不是异步拷贝不够？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：不能。异步拷贝也可能发出后立刻等它做完，效果和同步读一样；要看循环里 ttg.async_wait 的 num。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：看循环里 ttg.async_wait 的 num：大于 0 才说明等待时仍允许有拷贝在途；异步拷贝也可能发出后立刻等它做完，效果和同步读一样。
 • [T#B#有提前量]：循环里的等待是 num = 2 这类大于 0 的值，表示等的时候还允许有拷贝在途；循环开始前还有预先发出的拷贝。
 • [T#B#没有]：所有等待都是 num = 0、循环前也没有预先发出的拷贝：每轮发一次、等一次，没有任何提前量。
-• [T#B#实例]：练习里把 offset_n 在 K 循环里跨轮改写、写回又用了这个值的版本，flatten 开时就是这样；当时的测试只查“是不是异步拷贝”，没能发现。
+• [T#B#实例]：在 K 循环里给循环前已有的 offset_n 重新赋值、写回又直接用这个值的 kernel，flatten 开时就是这样；只查“是不是异步拷贝”的测试没能发现。
 [T#B,!c47f17#边界]：这个实例里流水为什么放弃提前量，没有读源码确认；现象由只编译的对照证实。</t>
         </is>
       </c>
@@ -244,13 +245,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">持久化矩阵乘里，每个 CTA 从自己的编号 pid 开始，以步长 NUM_SMS 循环领取 tile。有人把网格改成 4 × NUM_SMS 个 CTA，kernel 里的步长仍是 NUM_SMS。结果会怎样？怎样写才不会出这种错？</t>
+          <t xml:space="preserve">持久化矩阵乘里，NUM_SMS = 128，每个 CTA 从自己的编号 pid 开始，以步长 NUM_SMS 循环领取 tile。有人把网格改成 4 × NUM_SMS 个 CTA，kernel 里的步长仍是 NUM_SMS。结果会怎样？怎样写才不会出这种错？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：结果仍然正确，但大部分 tile 被重复计算和重复写入；步长必须等于实际发射的 CTA 数。
-• [T#B#现象]：网格 4 × 128 = 512 个 CTA、步长 128 时，编号 1000 的 tile 由 104、232、360、488 号 CTA 各算一次，总工作量约为原来的 3.95 倍。
+• [T#B#现象]：512 个 CTA、步长 128 时，编号 1000 的 tile 由 104、232、360、488 号 CTA 各算一次；编号 0–127 的 tile 算 1 次、128–255 算 2 次、256–383 算 3 次，其余都算 4 次，tile 远多于 512 个时总工作量接近 4 倍。
 • [T#B#难发现]：每次写入的值相同，数值测试全部通过，只是更慢。
 • [T#B#写法]：在 kernel 里用 tl.num_programs(0) 取步长，步长直接来自发射的网格，两者就不可能不一致。
 [T#B,!c47f17#边界]：教程用编译期常量 NUM_SMS，并由包装函数保证网格等于它；主机和 kernel 都要用的量，尽量只在一处产生。</t>
@@ -270,42 +271,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">给持久化矩阵乘的 tile 循环写了 flatten=True，程序运行正常、结果正确。凭什么判断循环合并真的生效了，而不是被编译器静默忽略？要看编译产物的哪几处？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 NVIDIA 后端上，给持久化矩阵乘的 tile 循环写了 flatten=True，程序运行正常、结果正确。凭什么判断循环合并真的生效了，而不是被编译器静默忽略？要看编译产物的哪几处？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：“没有报错”不算证据，合并条件不满足时编译器不报错；要看编译产物里合并留下的痕迹。
-• [T#B#条件分支]：TTGIR 里出现了原来没有的 scf.if，它们是合并后进入新 tile 和写回的两段。
-• [T#B#共享内存]：编译结果的 metadata.shared 比不合并时多一档，那是写回中转单独占用的缓冲。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：“没有报错”不算证据，合并条件不满足时编译器不报错。主证据是 TTGIR 里出现（或增多）了 scf.if，那是合并后按条件执行的分支。
 • [T#B#排空位置]：ttg.async_wait {num = 0} 从 tile 循环里面移到了整个合并循环之后，预热的拷贝也移到了循环之前。
+• [T#B#共享内存]：metadata.shared 通常比不合并时多一档，但只能作辅助：B 退回同步读入时它可能不增反减，合并后没有流水时它照样增加。
 • [T#B#取得途径]：kernel 调用返回编译结果对象，其 asm 按阶段存着 ttgir、ptx 等文本；也可以去缓存目录找，或只编译不运行。
-[T#B,!c47f17#边界]：这几处只说明合并发生了，不说明流水有提前量；后者要看循环里 ttg.async_wait 的 num 是否大于 0。</t>
+[T#B,!c47f17#边界]：这些判据来自 NVIDIA 后端：AMD gfx942 上合并生效时 scf.if 由 2 处变为 8 处，但没有异步拷贝可看，共享内存也不增加。合并发生了也不说明流水有提前量，后者要看循环里 ttg.async_wait 的 num 是否大于 0。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">scf.if 出现；共享内存多一档；排空移出循环</t>
+          <t xml:space="preserve">scf.if 出现是主证据；排空移出循环；共享内存只作辅助</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 3</t>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 3、练习 R-03 与 R-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 持久化矩阵乘教程在开了 flatten 的 kernel 里，除了领取 tile 的 tile_id，还给 epilogue 单独维护一个 tile_id_c，写回时用它重算坐标。为什么要这个独立游标？不写它会怎样？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，持久化矩阵乘教程在开了 flatten 的 kernel 里，除了领取 tile 的 tile_id，还给 epilogue 单独维护一个 tile_id_c，写回时用它重算坐标。为什么要这个独立游标？不写它会怎样？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：合并并流水之后，epilogue 执行时 tile_id 已经为后面的 tile 前进了；写回要用的是当前 tile 的坐标，所以要么自己维护一个落后的游标，要么由编译器替你保留旧值。
 • [T#B#教程的理由]：注释说 tile_id_c 用来打断 prologue 与 epilogue 之间的依赖，并规避 Blackwell 流水处理不了“一个值同时被 prologue 和 epilogue 使用”的缺陷。
-• [T#B#不写时]：源码语义由编译器保证：合并循环里会多带一份落后一步的 tile 坐标给写回用，结果仍然正确；sm_100 上去掉 tile_id_c 后每线程寄存器由 104 增到 114。
-[T#B,!c47f17#边界]：所以独立游标不是正确性所必需，而是减轻编译器负担、绕开缺陷；在 sm_89、sm_90、sm_120 上不写也能正确编译。</t>
+• [T#B#不写时]：按源码语义，编译器负责替你保留旧值：合并循环里会多带一份落后一步的 tile 坐标给写回用；去掉 tile_id_c 的副本在 sm_89、sm_90、sm_100 上都能编译，但更费寄存器。
+[T#B,!c47f17#边界]：所以独立游标主要是减轻编译器负担、绕开缺陷；教程所说的 Blackwell 流水缺陷会不会在 sm_100 上因此触发，只编译判断不了，没有在设备上验证。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -322,21 +322,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 持久化矩阵乘教程的 TMA 版，把 B 按 \[N, K\] 存放（沿 K 连续），而不是普通 a @ b 的 \[K, N\]。为什么这样摆？fp16 和 fp8 在这件事上有什么不同？</t>
+          <t xml:space="preserve">Triton 持久化矩阵乘教程的 TMA 版把 B 按 \[N, K\] 存放（沿 K 连续），而不是普通 a @ b 的 \[K, N\]。按 PTX ISA 9.4 与 Triton 3.7.1 的编译结果，为什么这样摆？如果 B 按 \[K, N\] 存放，fp16 与 fp8 各要付什么代价？</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：张量核心的乘加指令要沿 K 连续的操作数；按 \[N, K\] 存放的 B 正好沿 K 连续，搬进共享内存就能直接喂给指令。
-• [T#B#fp16]：wgmma 带转置立即数，可以接受 \[K, N\] 摆法的 B，所以 fp16 两种摆法都能直接用。
-• [T#B#fp8]：按 PTX ISA，wgmma 的转置只支持 f16 和 bf16；fp8 的 B 若是 \[K, N\]，Triton 仍能编译，但要先在寄存器里重排，多花寄存器和指令。
-• [T#B#读入]：B 沿 K 连续时，读一个 B 块也是沿 K 方向成段读取。
-[T#B,!c47f17#边界]：对 fp16 这是性能与通用性的选择，不是正确性要求；对 fp8 则是指令层面的硬性要求。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：乘加指令原生要的是沿 K 连续的操作数；按 \[N, K\] 存放的 B 搬进共享内存后正好沿 K 连续，不用转置就能喂给指令。\[K, N\] 摆法能不能补救、代价多大，取决于数据类型和指令。
+• [T#B#fp16]：sm_90 的 wgmma 带转置参数，\[K, N\] 摆法指令构成不变（sm_100 也相同）；sm_120 的 mma.sync 要多出转置读取（ldmatrix … trans），更费寄存器。
+• [T#B#fp8]：PTX ISA 规定 wgmma 的转置参数只支持 f16 和 bf16；sm_90 上 \[K, N\] 的 fp8 B 要先取进寄存器重排、再存回共享内存，多花寄存器和指令。
+[T#B,!c47f17#边界]：fp8 的这条硬性限制属于 sm_90 的 wgmma，不是张量核心指令的通则：sm_100 上 fp8 的两种摆法指令构成相同。</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">乘加要 K 连续；转置只给 f16 和 bf16</t>
+          <t xml:space="preserve">乘加要 K 连续；能否补救看指令：wgmma 的转置只给 f16 和 bf16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -374,7 +373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 持久化矩阵乘教程在 tl.where 把越界下标改成 0 之后，用 tl.max_contiguous 和 tl.multiple_of 声明下标“每 64 个一路加一”。可在跨过边界的那个 tile 里，例如 N = 208、第 3 号 tile 负责第 192–255 列，改写后是 192…207 再跟 48 个 0，声明并不成立。为什么这样写不会读错数，也不会越界？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，块宽 64 的 kernel 照教程的写法，在 tl.where 把越界下标改成 0 之后用 tl.max_contiguous(tl.multiple_of(offs, 64), 64) 声明下标每 64 个一路加一。可在跨过边界的那个 tile 里，例如 N = 208、第 3 号 tile 负责第 192–255 列，改写后是 192…207 再跟 48 个 0，声明并不成立。为什么这样写不会读错数，也不会越界？</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -400,7 +399,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">在 Triton kernel 里，下标经过 tl.where 后要恢复 16 字节的异步拷贝，常写 offs = tl.max_contiguous(tl.multiple_of(offs, 64), 64)。这两个函数各声明了什么？为什么只写其中一个不够？参数的值又有什么影响？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里，下标经过 tl.where 后要恢复 16 字节的异步拷贝，常写 offs = tl.max_contiguous(tl.multiple_of(offs, 64), 64)。这两个函数各声明了什么？为什么只写其中一个不够？</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -408,8 +407,8 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：一次搬 16 字节要同时满足两件事：8 个元素一路加一，并且起点 16 字节对齐；max_contiguous 管前一件，multiple_of 管后一件。
 • [T#B#max_contiguous]：声明张量能切成每 C 个一组、组内一路加一的段。
 • [T#B#multiple_of]：声明每组第一个元素是 D 的倍数；整数下标按元素算，指针按字节算，tl.multiple_of(ptr, 16) 就是 16 字节对齐。
-• [T#B#实测]：tl.where 之后只写其中一条，都退回逐元素同步读；两条都写成 64 才是 16 字节；任一个写成 4，一次只能搬 4 个 fp16，即 8 字节。
-[T#B,!c47f17#边界]：声明只描述这一个张量：行步长 N 不是 16 的倍数时行首对不齐，声明写满也只能逐元素读；参数必须是编译期整数，取 2 的幂。</t>
+• [T#B#实测]：tl.where 之后只写其中一条，都退回逐元素同步读；两条都写、块宽 64 时写成 64，得到 16 字节一组；任一个写成 4，一次只能搬 4 个 fp16，即 8 字节。
+[T#B,!c47f17#边界]：声明只描述这一个张量：行步长 N 不是 16 的倍数时行首对不齐，声明写满也只能逐元素读。</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -426,7 +425,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一个 Triton 矩阵乘 kernel，用 N = 208 和 N = 1024 调用时共用一份编译结果，用 N = 200 调用时却重新编译，而且 B 的读入退回逐元素。Triton 发射 kernel 时对整数和指针实参做了什么？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中，同一个矩阵乘 kernel 用 N = 208 和 N = 1024 调用时共用一份编译结果，用 N = 200 调用时却重新编译，而且 B 的读入退回逐元素。发射 kernel 时 Triton 对整数和指针实参做了什么？</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -452,36 +451,10 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">块 128 × 128 × 64、fp16 的矩阵乘，一轮 K 循环在 sm_89 与 sm_120（mma.sync）、sm_90（wgmma）、sm_100（tcgen05.mma）上，分别由谁发出乘加指令、一条指令算多大、一轮要几条？</t>
+          <t xml:space="preserve">描述符版的持久化矩阵乘，写回 C 前要把整块结果放进共享内存；把输出块切成左右两半分两次写回（epilogue 拆半），输出缓冲就只要一半。拆半什么时候能换来多一级流水？用 sm_120（每个 CTA 上限 101,376 字节）、块 128 × 128 × 64 fp16、4 个 stage 判断。</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：三代指令的粒度越来越大、发起者越来越少：mma.sync 按 warp，wgmma 按 4 个 warp 组成的 warpgroup，tcgen05.mma 由一个线程发起。
-• [T#B#mma.sync]：形状 m16n8k16，每个 warp 算输出的 16 × 8 一小片、沿 K 吃 16 个元素；8 个 warp 时每个 warp 每轮 64 条，操作数和累加器都在寄存器里。
-• [T#B#wgmma]：形状 m64n128k16，一个 warpgroup 算 64 行，两个 warpgroup 各算一半，每轮 4 条；操作数可以直接从共享内存读。
-• [T#B#tcgen05.mma]：一条算 128 × 128 × 16，由一个线程发起，每轮 4 条；累加器放在张量核心专用的 TMEM 里。
-[T#B,!c47f17#边界]：sm_120 虽是新一代，乘加仍用 mma.sync，没有 wgmma 和 tcgen05。</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">m16n8k16 按 warp；m64n128k16 按 warpgroup；128×128×16 由一个线程发起</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">描述符版的持久化矩阵乘，写回 C 前要把整块结果放进共享内存；把输出块切成左右两半分两次写回（epilogue 拆半），输出缓冲就只要一半。拆半什么时候能换来多一级流水？用 sm_120（每个 CTA 上限 101,376 字节）、块 128 × 128 × 64 fp16、4 个 stage 判断。</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：拆半省的是半个输出块，多一级流水要的是 A、B 各一个块；省下的够不够，要拿它和超出上限的量比较。
 • [T#B#本例]：4 个 stage 不拆半要 131,096 字节，拆半后 114,712，省了 16,384，但仍超上限 13,336，换不来第 4 个 stage。
@@ -490,24 +463,24 @@
 [T#B,!c47f17#边界]：指针版写回前同样要经过共享内存换布局，flatten 开时同样受益于拆半；代价是两次写回和一次累加器重排。</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">省半个输出块 vs 要一个 A 块加一个 B 块</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 6</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 Triton kernel 里手写一个合并循环：循环体里 if k == 0: 时计算 offset_m，if 之后的每一轮都用 offset_m 算地址。用 TRITON_INTERPRET=1 跑解释器全部正确，正式编译却报 NameError('offset_m is not defined')。为什么？</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 的 kernel 里手写一个合并循环：循环体里 if k == 0: 时计算 offset_m，if 之后的每一轮都用 offset_m 算地址。用 TRITON_INTERPRET=1 跑解释器全部正确，正式编译却报 NameError('offset_m is not defined')。为什么？</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：编译时 Triton 生成 SSA 形式的 IR：只在 if 里第一次赋值的名字，出了 if 就不存在；解释器按 Python 执行，名字一直留着，所以不报错。
 • [T#B#if 规则]：if 之后看得见的只有进 if 之前就有的名字，或两个分支都赋了值的名字。
@@ -515,24 +488,24 @@
 [T#B,!c47f17#边界]：所以解释器层通过不等于能编译；循环合并也不必手写，在 tl.range 上写 flatten=True 由编译器生成。</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">if 内首次赋值的名字出 if 即消失；解释器不检查</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 练习 R-02</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">实测比较“每个 CTA 一个 tile”（4096 个 CTA）与“每个 SM 一个持久 CTA”（170 个，循环领取 tile）两种调度，两者用同一个 kernel、都不开 flatten。它们的时间比衡量的是“持久化本身”，但这个净效果里包含哪几项变化？能否据此断定收益来自发射开销？</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：包含三项：硬件分派与回收的 CTA 数（4096 对 170）、每个 CTA 进入 tile 循环前的固定工作、tile 分到 SM 的方式（硬件动态分派对固定步长的静态领取）；这一列只给出三项的净和。
 • [T#B#不变的]：每个 tile 都要计算一次编号和坐标、执行一次循环控制，两种调度下相同，不算差别。
@@ -540,14 +513,168 @@
 [T#B,!c47f17#边界]：所以不能断定收益来自发射开销；要拆开，需要 profiler 时间线或单独测量空 kernel 的发射开销。</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">分派、固定工作、调度方式；只有净和</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 RTX 5090（sm_120）上用 Triton 3.7.1 实测：K = 2048 时，持久化矩阵乘开 flatten 反而比不开慢。开 flatten 的版本共享内存 73,728 字节、每线程 154 个寄存器，不开的是 65,536 字节、182 个，都没有寄存器溢出；每个 CTA 256 个线程，每个 SM 有 65,536 个寄存器。能否用“多用共享内存、少用寄存器”解释它变慢？应该先算什么？</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能直接这么解释，要先算每个 SM 能驻留几个 CTA。没有寄存器溢出时，资源用量主要通过驻留数影响速度；这里两个版本都只驻留 1 个 CTA，资源差别没有改变并行度。
+• [T#B#寄存器]：两个 CTA 至少要 2 × 154 × 256 = 78,848 个寄存器（不开 flatten 时 2 × 182 × 256 = 93,184 个），都超过 65,536，放不下第二个 CTA。
+• [T#B#共享内存]：两个 CTA 需要 131,072 字节以上的共享内存，同样放不下；多出的 8,192 字节没有改变驻留数。
+• [T#B#前提]：寄存器溢出到本地内存时，驻留数不变也会变慢，所以看驻留数之前先确认没有溢出。
+[T#B,!c47f17#边界]：flatten 在大 K 下代价的真正来源没有验证，一个未验证的假设是合并后每轮都要做的判断。</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">分派、固定工作、调度方式；只有净和</t>
+          <t xml:space="preserve">先确认无溢出，再算驻留数；驻留数不变，资源差别就不是主因</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，把教程里“持久化 + flatten”的指针版矩阵乘移到没有 cp.async、也没有 TMA 的后端（例如 AMD gfx942 / CDNA3）上。持久化、flatten、TMA／TMEM／warp 专用化这三层收益各还剩下什么？flatten 的收益取决于什么？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：持久化原样保留；flatten 的合并照样发生，能否带来收益取决于后端的流水能不能让读入在后台进行，而不在于有没有 cp.async 这条指令；TMA、TMEM 和 warp 专用化依赖硬件，没有就退掉。
+• [T#B#持久化]：它由手写的 tile 循环和包装函数的网格决定，不依赖任何硬件特性，省掉的发射与退出照样省。
+• [T#B#flatten]：gfx942 上合并生效（scf.if 由 2 处变为 8 处）；没有异步拷贝指令，读入先取进寄存器再存进共享内存，但仍提前一轮发出，每个操作数仍是 2 个槽，共享内存也不增加。
+• [T#B#先看什么]：先看产物里流水有没有把下一轮、下一个 tile 的读入提前发出，再判断 flatten 值不值得开；不能拿 NVIDIA 上“共享内存多一档、排空等待移出循环”的现象来判断。
+[T#B,!c47f17#边界]：以上是只编译的观察，没有在 AMD 设备上运行，收益大小未知。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化不靠硬件；flatten 看读入能否在后台进行；TMA、TMEM、专用化随硬件走</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 综合验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘（每个 SM 一个 CTA、循环领取 tile）和 Triton 的 flatten，相对逐 tile 发射的收益来自哪里？据此说明：什么情况下收益为零或得不偿失，tile 数和 K 又怎样影响收益的比例。</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：收益只来自 tile 之间的间隔（重复的发射与退出、每个 tile 等第一批数据的空档），间隔占总时间的比例越小，收益越小：tile 数不多于 SM 数时收益为零；K 越大、每个 CTA 分到的 tile 越少，收益越小。
+• [T#B#tile 不够多]：例如 M = N = 1024、块 128 只有 64 个 tile，而 SM 有 128 个：持久版也只发射 64 个 CTA、各做一个 tile，与逐 tile 发射等价；一半 SM 空着，该调的是块大小而不是调度方式。flatten 在这里只剩代价，共享内存照样多一档。
+• [T#B#K]：K 越大，K 循环越长而 tile 之间的固定间隔不变，间隔的占比下降；K = 128 比 1024 的提速比例大。
+• [T#B#tile 数]：每个 CTA 分到的 tile 越多，间隔越多：32 个 tile 有 31 个间隔，2 个只有 1 个，被省掉的发射分别占 31/32 和 1/2。
+• [T#B#实测]：RTX 5090 上的受控测量里，持久化本身最多 2.3%；flatten 到 K = 2048 已是净代价。
+[T#B,!c47f17#边界]：flatten 在大 K 下代价的来源没有验证；一个未验证的假设是合并后每一轮都要做的“是否进入新 tile、是否写回”的判断。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收益看间隔占比；tile 不多于 SM 时为零；大 K 时 flatten 可能是净代价</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 1–2、M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，给持久化矩阵乘的 tile 循环开 flatten=True、合并生效后，编译结果的共享内存比不合并时多出一块。多出的是什么？为什么不合并时不需要单独给它一块？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：多出的是 epilogue 写回前换布局用的中转缓冲：不合并时它可以借用已经空出的输入槽，合并后输入槽在 epilogue 期间仍被下一个 tile 的读入占着，只能单独占一块。
+• [T#B#不合并]：tile 的 K 循环结束时流水已经排空，输入缓冲不再使用；epilogue 把累加器从乘加的布局换成写回的布局时，中转可以和它们共用同一段共享内存。
+• [T#B#合并后]：epilogue 执行时，下一个 tile 的头几轮读入已经在路上，输入槽还被占着；两块缓冲同时在用，编译器只能给中转另分一块。
+[T#B,!c47f17#边界]：正因为合并后这块中转单独存在，把 epilogue 拆成两半写回，在 flatten 开时对指针版同样能省共享内存（sm_89 上 98,304 → 81,920 字节）。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中转借不到输入槽：下一个 tile 的读入已在路上</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 3、节点 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 Triton 3.7.1 中，持久化矩阵乘教程在 sm_90（Hopper）上启用 warp 专用化时，把 tile 循环的 flatten 关掉。为什么两者在 sm_90 上不能同时开？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不是硬件限制，也不是 warp 分化：这个版本的 Hopper 专用化 pass 遇到带非空 else 块的 scf.if 就直接放弃（源码标着 FIXME），而循环合并后必然出现这样的 scf.if。
+• [T#B#为何必有 else]：合并后“进入新 tile”的那个 if 要产出新的 tile 编号和偏移；不进 if 的各轮也得有值，就沿用旧值，所以它在 IR 里是 if … else { 沿用旧值 }，相当于 C 的 x = cond ? 新值 : 旧值。
+• [T#B#另一前提]：同一处源码还要求恰好 4 个 warp：写 8 个时 warp_specialize=True 被忽略，产物不变，也不报错。
+[T#B,!c47f17#边界]：关掉 flatten 并不丢掉跨 tile 的预取：专用化后的搬运分区有自己的循环，只等空槽，自然跨过 tile 边界。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合并必带 else 的 scf.if；3.7.1 的 Hopper 专用化遇到 else 就放弃</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在 sm_100（Blackwell）上，tcgen05.mma 把累加器写在 TMEM 里。按 PTX ISA 9.4，TMA 能不能直接把结果从 TMEM 搬到显存？写回 C 的数据要依次经过哪里？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：不能：TMA 只在显存与共享内存之间搬。结果要先由线程读回寄存器，再写进共享内存，最后由 TMA 写到显存。
+• [T#B#TMEM 出入口]：TMEM 只能用 tcgen05 自己的指令读写（tcgen05.ld、tcgen05.st、tcgen05.cp），epilogue 用 tcgen05.ld 把累加器读进寄存器。
+• [T#B#共享内存]：TMA 只能从共享内存搬，所以 sm_100 的描述符版写回前仍要一块共享内存输出缓冲。
+[T#B,!c47f17#边界]：这条路径来自 PTX 文档与 Triton 3.7.1 的只编译产物，没有在设备上测过这段写回的耗时。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TMA 只连显存与共享内存：TMEM → 寄存器 → 共享内存 → 显存</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化矩阵乘学习记录 10-14 · 节点 5–6</t>
         </is>
       </c>
     </row>
